--- a/assets/docs/lop4/Khoa hoc - Lop 4.xlsx
+++ b/assets/docs/lop4/Khoa hoc - Lop 4.xlsx
@@ -748,7 +748,8 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Sau khi các nhóm làm thí nghiệm với túi ni lông và chậu nước, HS ghi kết quả vào bảng chiếu trên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Mở đầu bài “Không khí có ở đâu?”, GV chiếu đoạn phim hoạt hình về không khí xung quanh ta, dừng hình ở cảnh bong bóng khí nổi lên trong nước
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau khi các nhóm làm thí nghiệm với túi ni lông và chậu nước, HS ghi kết quả vào bảng chiếu trên màn hình; khi nhóm nào ra kết quả khác</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1287,8 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài “Nhiệt độ và sự truyền nhiệt”, GV chiếu ảnh phóng to mặt nhiệt kế.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Nhiệt độ và sự truyền nhiệt”, GV chiếu ảnh phóng to mặt nhiệt kế để cả lớp cùng đọc đúng số chỉ
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả đo vào bảng chiếu trên màn hình rồi cùng đối chiếu; khi số liệu các nhóm khác nhau, cả lớp tìm nguyên nhân là đặt nhiệt kế gần cửa sổ</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1352,8 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): HS ghi kết quả thí nghiệm vào bảng chiếu trên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài vật dẫn nhiệt tốt và vật dẫn nhiệt kém, GV chiếu mô phỏng nhiệt truyền qua thìa kim loại và thìa gỗ cắm trong cốc nước nóng
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả thí nghiệm vào bảng chiếu trên màn hình rồi đối chiếu với dự đoán; khi kết quả các nhóm khác nhau</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop4/Khoa hoc - Lop 4.xlsx
+++ b/assets/docs/lop4/Khoa hoc - Lop 4.xlsx
@@ -2728,11 +2728,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Tổng kết môn học, GV chiếu sơ đồ các chủ đề đã học trong năm lên màn hình, mở.</t>
-        </is>
-      </c>
+      <c r="H73" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/assets/docs/lop4/Khoa hoc - Lop 4.xlsx
+++ b/assets/docs/lop4/Khoa hoc - Lop 4.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -661,7 +661,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -761,7 +761,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
